--- a/naver-place-crawler/results_nail/하남_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/하남_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V123"/>
+  <dimension ref="A1:V153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11853,34 +11853,30 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>속눈썹증모,연장</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1022뷰티살롱</t>
+          <t>손끝정원</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>naillash@naver.com</t>
+          <t>yeojuhangul@naver.com</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>0507-1335-9769</t>
-        </is>
-      </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변대로 80 그린프라자 2층 206호</t>
+          <t>경기도 하남시 미사강변서로 25 1층 알121호</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/naillash</t>
+          <t>https://www.instagram.com/fingertip_garden_nail</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -11895,7 +11891,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -11906,7 +11902,7 @@
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -11915,30 +11911,2826 @@
         </is>
       </c>
       <c r="P123" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>24</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>2090363651</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2090363651</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>오브제네일</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>bilandjin@naver.com</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로 190 롯데캐슬스타 2층 255호</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_FixiyG</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>222</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>20</v>
+      </c>
+      <c r="R124" t="n">
+        <v>242</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>1916861263</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1916861263</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>루미가넷네일존 하남점</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>barbie55555@naver.com</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>0507-1352-9415</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>경기도 하남시 덕풍서로 70 1층</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>14</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>1682321121</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1682321121</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>오브니 네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>bongbong323@naver.com</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>031-553-5240</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변서로 16 하우스디스마트밸리 R108호 오브니네일스튜디오</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ovni_nail</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>10</v>
+      </c>
+      <c r="R126" t="n">
+        <v>25</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>1829391097</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1829391097</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>리본네일</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>bongbong323@naver.com</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>0507-1435-3409</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>경기도 하남시 감일중앙로 60 감일벨솔레파크 3층 318호</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rebornnail3390?igsh=MW9wajFmYTNocnE2dw%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>321</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>4</v>
+      </c>
+      <c r="R127" t="n">
+        <v>325</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>1418199556</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1418199556</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>솔핑네일</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>seoji_15@naver.com</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>0507-1386-7713</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변동로 125 A동 2층 A-233호</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_gxeJnn</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>332</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>3</v>
+      </c>
+      <c r="R128" t="n">
+        <v>335</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>1456488337</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1456488337</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>엘네일</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>dalmee0224@naver.com</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>경기도 하남시 하남대로 815 명지캐럿108 118호</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/aeri_l.nail</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>7</v>
+      </c>
+      <c r="R129" t="n">
+        <v>31</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>1141972371</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1141972371</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>도나쓰샵 미사점</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>donnas__shop@naver.com</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>0507-1383-0372</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변한강로158번안길 34 1층 104호</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/donnas__shop</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>386</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>46</v>
+      </c>
+      <c r="R130" t="n">
+        <v>432</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>1852621964</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1852621964</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>네일오브휴 하남본점</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>of_hue@naver.com</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>0507-1394-1432</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>경기도 하남시 하남유니온로 23 1층 네일오브휴</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_of.hue</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>127</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>3</v>
+      </c>
+      <c r="R131" t="n">
+        <v>130</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>1072946741</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1072946741</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>위치네일스 스타필드하남점</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>witch_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>031-8072-8506</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사대로 750 스타필드 하남 B1</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/witch_nail</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>383</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>69</v>
+      </c>
+      <c r="R132" t="n">
+        <v>452</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>38502592</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38502592</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>뷰티플러스</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>beautyplus9433@naver.com</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>0507-1382-9433</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>경기도 하남시 감일로124번길 11 101호</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/beautyplus9433</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>1</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>1845701974</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1845701974</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>네일ddd</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>nail_d_d_d@naver.com</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>0507-1442-3698</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변동로 95 2층 2095호</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_d_d_d</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>659</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>36</v>
+      </c>
+      <c r="R134" t="n">
+        <v>695</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>1016876522</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1016876522</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>수네일</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>yjh1000j@naver.com</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>0507-1406-0537</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>경기도 하남시 위례대로 220 상가동 제 1층 113호</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_ssunail</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>766</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>6</v>
+      </c>
+      <c r="R135" t="n">
+        <v>772</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>1344624985</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1344624985</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>앙루미네일 미사본점</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>younga8982@naver.com</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>0507-1408-4973</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로 212 안강프라이빗뷰 4층 401호</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/anglumi__nail</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>7</v>
+      </c>
+      <c r="R136" t="n">
+        <v>173</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>2001664787</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2001664787</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>그리니네일</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>argentline@naver.com</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>0507-1489-9400</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로 161 3층 308호</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/greenee_nail?igsh=OGQ5ZDc2ODk2ZA%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>321</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>13</v>
+      </c>
+      <c r="R137" t="n">
+        <v>334</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>1203096131</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1203096131</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>네일로그</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>nail_log@naver.com</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>0507-1349-0853</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사대로 520 현대지식산업센터 2차 C동 347호</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>1</v>
+      </c>
+      <c r="R138" t="n">
+        <v>121</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>1437448868</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1437448868</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>네일두이</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>odk1011@naver.com</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>0507-1406-1418</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변동로 100-1 2층 2053호</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>8</v>
+      </c>
+      <c r="R139" t="n">
+        <v>96</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>1889054284</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1889054284</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>우브네일</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>s_shua@naver.com</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로 190 하남미사롯데캐슬스타 2층 244호</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>https://zero.gongbiz.kr/shop/S000028965</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>477</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>55</v>
+      </c>
+      <c r="R140" t="n">
+        <v>532</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>1466919251</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1466919251</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>네일바이주</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>tlrdl7744@naver.com</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>0507-1313-0353</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>경기도 하남시 감일백제로83번길 25 숲83 4층</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nail.by.joo</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>745</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>9</v>
+      </c>
+      <c r="R141" t="n">
+        <v>754</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>1332721594</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1332721594</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>더먀오네일룸</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>lovesami@naver.com</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>0507-1411-3204</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로204번길 45 성산타워플러스 601호</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/noga_themyao</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>371</v>
+      </c>
+      <c r="R142" t="n">
+        <v>1646</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>37296896</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37296896</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>쏘네일 미사점</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>linara_tarasova_77@naver.com</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>0507-1442-0527</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변동로 73 노블레스빌딩 5층 521호 SSO NAIL</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_jDwPC</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>165</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>32</v>
+      </c>
+      <c r="R143" t="n">
+        <v>197</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>1735469799</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1735469799</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>모몽네일 스튜디오</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>momongnail_studio@naver.com</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>0507-1454-7832</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변한강로 270-1 미사호반써밋 상가 2층 135호</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_RLyxon</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>5</v>
+      </c>
+      <c r="R144" t="n">
+        <v>33</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>2084580317</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2084580317</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>제이원네일</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>dooyou1@naver.com</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>0507-1374-8723</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>경기도 하남시 대청로116번길 59-1 꿈동산신안아파트 1층102호, 2층225호</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dooyou1</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" t="n">
+        <v>114</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>1556395771</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1556395771</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>아르떼뷰티앤 레푸스 하남1호점</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>h930267@naver.com</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>0507-1412-8528</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>경기도 하남시 덕풍동로 111-50 트윈렉스 2동 204호</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@refuss_hanam</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>921</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>364</v>
+      </c>
+      <c r="R146" t="n">
+        <v>1285</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>36932744</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36932744</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>그리다네일</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>gridanail2@naver.com</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>경기도 하남시 신장로136번길 12 1층</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/grida_nail.v</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>169</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>5</v>
+      </c>
+      <c r="R147" t="n">
+        <v>174</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>1945540707</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1945540707</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>후유네일</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>pe1052@naver.com</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>경기도 하남시 위례학암로14번길 11 406호</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hooyoonail</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>8</v>
+      </c>
+      <c r="R148" t="n">
+        <v>53</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>1524535921</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1524535921</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>네일해,별</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>like8017@naver.com</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변남로 33 황금프라자 1층 네일해별</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailsun_star</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>349</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>62</v>
+      </c>
+      <c r="R149" t="n">
+        <v>411</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>1254657413</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1254657413</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>네일밤 미사점</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>hyunzero7@naver.com</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>0507-1342-6431</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변동로 100-1 (미사역파라곤스퀘어) 2층 2066호</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail__bam0</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>330</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>15</v>
+      </c>
+      <c r="R150" t="n">
+        <v>345</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>1606647844</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1606647844</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>인마이뷰티네일</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>luv1007_@naver.com</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>0507-1311-3624</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변동로 121 더랜드시티 2층 206호 인마이뷰티</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>http://instagram.com/inmybeauty_nail</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>146</v>
+      </c>
+      <c r="R151" t="n">
+        <v>306</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>1283283849</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1283283849</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>네일앤초이</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>nail__choi@naver.com</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>0507-1445-3282</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>경기도 하남시 감일백제로 109 M타워감일 3층 307호</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail__choi</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>418</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>9</v>
+      </c>
+      <c r="R152" t="n">
+        <v>427</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>1942301068</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1942301068</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>속눈썹증모,연장</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1022뷰티살롱</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>naillash@naver.com</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>0507-1335-9769</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변대로 80 그린프라자 2층 206호</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/naillash</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
         <v>112</v>
       </c>
-      <c r="Q123" t="n">
+      <c r="Q153" t="n">
         <v>91</v>
       </c>
-      <c r="R123" t="n">
+      <c r="R153" t="n">
         <v>203</v>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T123" t="inlineStr">
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
         <is>
           <t>1683892292</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="U153" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1683892292</t>
         </is>
       </c>
-      <c r="V123" t="inlineStr">
+      <c r="V153" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
